--- a/Data.xlsx
+++ b/Data.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Git_Upload\Food_Equity_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB83FF4-9441-46EB-B2DB-BD9033E83569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10449789-408A-492D-83A9-6C526CA6AB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -220,24 +231,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -570,12 +581,12 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="F1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
       <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
@@ -599,19 +610,19 @@
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
       <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="13" t="b">
+      <c r="M2" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -628,27 +639,27 @@
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+      <c r="F3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
       <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="13" t="b">
+      <c r="M3" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -660,25 +671,25 @@
       <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
+      <c r="F4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
       <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="13" t="b">
+      <c r="M4" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
@@ -688,25 +699,25 @@
       <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="F5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
       <c r="J5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="13" t="b">
+      <c r="M5" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
@@ -716,23 +727,23 @@
       <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="F6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
       <c r="J6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="6"/>
-      <c r="M6" s="13" t="b">
+      <c r="M6" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
@@ -742,25 +753,25 @@
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="F7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
       <c r="J7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="13" t="b">
-        <v>0</v>
+      <c r="M7" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
@@ -770,12 +781,12 @@
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="F8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
       <c r="J8" s="2" t="s">
         <v>7</v>
       </c>
@@ -785,15 +796,15 @@
       <c r="L8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="13" t="b">
-        <v>0</v>
+      <c r="M8" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -805,12 +816,12 @@
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="F9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
       <c r="J9" s="2" t="s">
         <v>7</v>
       </c>
@@ -818,13 +829,13 @@
       <c r="L9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="13" t="b">
-        <v>0</v>
+      <c r="M9" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
@@ -849,8 +860,8 @@
       <c r="K10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="13" t="b">
-        <v>0</v>
+      <c r="M10" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -872,7 +883,7 @@
       <c r="K11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M11" s="13" t="b">
+      <c r="M11" s="9" t="b">
         <v>0</v>
       </c>
     </row>
